--- a/reports/pdf_change_20260827.xlsx
+++ b/reports/pdf_change_20260827.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,575억   ·   현금 33억(0.7%)      당일 2026-08-27  vs  전영업일 2026-08-26      매수 2종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,575억      당일 2026-08-27  vs  전영업일 2026-08-26      매수 2종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -891,7 +891,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,904억   ·   현금 12억(0.3%)      당일 2026-08-27  vs  전영업일 2026-08-26      매수 5종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,904억      당일 2026-08-27  vs  전영업일 2026-08-26      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1168,7 +1168,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,577억   ·   현금 33억(1.3%)      당일 2026-08-27  vs  전영업일 2026-08-26      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,577억      당일 2026-08-27  vs  전영업일 2026-08-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1192,7 +1192,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,256억   ·   현금 32억(1.4%)      당일 2026-08-27  vs  전영업일 2026-08-26      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,256억      당일 2026-08-27  vs  전영업일 2026-08-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1216,7 +1216,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 2억(0.7%)      당일 2026-08-27  vs  전영업일 2026-08-26      매수 5종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억      당일 2026-08-27  vs  전영업일 2026-08-26      매수 5종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1525,7 +1525,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 561억   ·   현금 3억(0.5%)      당일 2026-08-27  vs  전영업일 2026-08-26      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 561억      당일 2026-08-27  vs  전영업일 2026-08-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>

--- a/reports/pdf_change_20260827.xlsx
+++ b/reports/pdf_change_20260827.xlsx
@@ -840,23 +840,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-771790500</v>
+        <v>-182087100</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.88%→2.66%</t>
+          <t>0.55%→0.48%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>50→47</t>
+          <t>39→36</t>
         </is>
       </c>
     </row>
@@ -868,23 +868,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-182087100</v>
+        <v>-771790500</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.55%→0.48%</t>
+          <t>2.88%→2.66%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>39→36</t>
+          <t>50→47</t>
         </is>
       </c>
     </row>
